--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513652_FASEFINALAFFA1_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513652_FASEFINALAFFA1_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3311</v>
+        <v>6.624</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9893</v>
+        <v>7.9482</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6581</v>
+        <v>-1.3242</v>
       </c>
       <c r="G2" t="n">
         <v>9.6828</v>
@@ -610,13 +610,13 @@
         <v>1.1684</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.009</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2985</v>
+        <v>-0.3396</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7105</v>
+        <v>-0.3766</v>
       </c>
       <c r="V2" t="n">
         <v>1.5521</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6435</v>
+        <v>2.4811</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4728</v>
+        <v>3.3939</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8294</v>
+        <v>-0.9129</v>
       </c>
       <c r="G3" t="n">
         <v>3.4979</v>
@@ -688,13 +688,13 @@
         <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2176</v>
+        <v>-0.38</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8657</v>
+        <v>0.0554</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3519</v>
+        <v>-0.4354</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2211</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0883</v>
+        <v>0.2804</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3322</v>
+        <v>2.3727</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2439</v>
+        <v>-2.0923</v>
       </c>
       <c r="G4" t="n">
-        <v>0.254</v>
+        <v>1.7155</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1673</v>
+        <v>2.6016</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4213</v>
+        <v>-0.8862</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2013</v>
+        <v>3.7389</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0392</v>
+        <v>3.7949</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1621</v>
+        <v>-0.056</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9473</v>
+        <v>-2.0235</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2065</v>
+        <v>-1.1933</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2592</v>
+        <v>-0.8302</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1947</v>
+        <v>-2.921</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1947</v>
+        <v>-3.3105</v>
       </c>
       <c r="R4" t="n">
         <v>0.3895</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5812</v>
+        <v>-0.0145</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0462</v>
+        <v>0.1643</v>
       </c>
       <c r="U4" t="n">
-        <v>0.535</v>
+        <v>-0.1788</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9416</v>
+        <v>1.5005</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2795</v>
+        <v>1.78</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2211</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0322</v>
+        <v>0.1664</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4862</v>
+        <v>1.4937</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4541</v>
+        <v>-1.3273</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7155</v>
+        <v>0.254</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6016</v>
+        <v>-0.1673</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8862</v>
+        <v>0.4213</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7389</v>
+        <v>1.2013</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7949</v>
+        <v>1.0392</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.056</v>
+        <v>0.1621</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0235</v>
+        <v>-0.9473</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1933</v>
+        <v>-1.2065</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8302</v>
+        <v>0.2592</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.921</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3105</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
         <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2628</v>
+        <v>0.6592</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2778</v>
+        <v>0.2077</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5406</v>
+        <v>0.4515</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5005</v>
+        <v>-0.9416</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8901</v>
+        <v>-0.6073</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0229</v>
+        <v>0.1765</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8672</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6044</v>
@@ -922,13 +922,13 @@
         <v>0.3895</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3957</v>
+        <v>-0.1128</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1855</v>
+        <v>0.0138</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2102</v>
+        <v>-0.1267</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2795</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4567</v>
+        <v>-2.1932</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3328</v>
+        <v>-1.7075</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1239</v>
+        <v>-0.4856</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8062</v>
@@ -1000,13 +1000,13 @@
         <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3495</v>
+        <v>-0.3869</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4633</v>
+        <v>0.0886</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1138</v>
+        <v>-0.4756</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6105</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.84</v>
+        <v>-4.2642</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7591</v>
+        <v>-3.072</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0809</v>
+        <v>-1.1922</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2844</v>
@@ -1078,13 +1078,13 @@
         <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7481</v>
+        <v>0.3239</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6331</v>
+        <v>0.3203</v>
       </c>
       <c r="U8" t="n">
-        <v>0.115</v>
+        <v>0.0037</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9932</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.566</v>
+        <v>-5.2173</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0876</v>
+        <v>-2.5998</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4783</v>
+        <v>-2.6175</v>
       </c>
       <c r="G9" t="n">
         <v>-4.9153</v>
@@ -1156,13 +1156,13 @@
         <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7388</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8187</v>
+        <v>0.3064</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0799</v>
+        <v>-0.219</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.657699999999998</v>
+        <v>-2.7301</v>
       </c>
       <c r="E10" t="n">
-        <v>7.0781</v>
+        <v>8.005700000000001</v>
       </c>
       <c r="F10" t="n">
         <v>-10.7358</v>
@@ -1234,10 +1234,10 @@
         <v>5.8421</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4675</v>
+        <v>-0.5399</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1106</v>
+        <v>0.8169000000000001</v>
       </c>
       <c r="U10" t="n">
         <v>-1.3569</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8791</v>
+        <v>4.4396</v>
       </c>
       <c r="E11" t="n">
-        <v>5.0194</v>
+        <v>3.5243</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8597</v>
+        <v>0.9154</v>
       </c>
       <c r="G11" t="n">
         <v>1.2253</v>
@@ -1312,13 +1312,13 @@
         <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2964</v>
+        <v>0.8569</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4199</v>
+        <v>0.9248</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1235</v>
+        <v>-0.0678</v>
       </c>
       <c r="V11" t="n">
         <v>2.1626</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3475</v>
+        <v>4.1165</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8431</v>
+        <v>2.946</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5044</v>
+        <v>1.1705</v>
       </c>
       <c r="G12" t="n">
         <v>0.6569</v>
@@ -1390,13 +1390,13 @@
         <v>2.7263</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3274</v>
+        <v>1.0964</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4306</v>
+        <v>0.5335</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8969</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.6105</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2032</v>
+        <v>3.6767</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3319</v>
+        <v>4.3694</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1287</v>
+        <v>-0.6927</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7523</v>
+        <v>1.2276</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9633</v>
+        <v>1.2973</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.211</v>
+        <v>-0.0697</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2878</v>
+        <v>3.6116</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2067</v>
+        <v>1.7551</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08110000000000001</v>
+        <v>1.8565</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5354</v>
+        <v>-2.384</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2434</v>
+        <v>-0.4578</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.292</v>
+        <v>-1.9262</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1947</v>
+        <v>2.5316</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1684</v>
+        <v>2.5316</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3661</v>
+        <v>-0.4135</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1278</v>
+        <v>-0.4633</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2383</v>
+        <v>0.0498</v>
       </c>
       <c r="V13" t="n">
-        <v>0.89</v>
+        <v>0.3311</v>
       </c>
       <c r="W13" t="n">
-        <v>0.89</v>
+        <v>1.2211</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5571</v>
+        <v>2.1832</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4723</v>
+        <v>2.5345</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9153</v>
+        <v>-0.3514</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2276</v>
+        <v>0.7523</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2973</v>
+        <v>0.9633</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0697</v>
+        <v>-0.211</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6116</v>
+        <v>2.2878</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7551</v>
+        <v>2.2067</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8565</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.384</v>
+        <v>-1.5354</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4578</v>
+        <v>-1.2434</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9262</v>
+        <v>-0.292</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5316</v>
+        <v>0.1947</v>
       </c>
       <c r="Q14" t="n">
+        <v>-0.9737</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.1684</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.5316</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-1.5332</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-1.3604</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.1728</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.3311</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2211</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.89</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9339</v>
+        <v>0.774</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4345</v>
+        <v>1.1355</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5006</v>
+        <v>-0.3615</v>
       </c>
       <c r="G15" t="n">
         <v>0.3608</v>
@@ -1624,13 +1624,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5994</v>
+        <v>0.4395</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7725</v>
+        <v>0.4735</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1731</v>
+        <v>-0.0339</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6105</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2723</v>
+        <v>0.2377</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3956</v>
+        <v>1.7943</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6679</v>
+        <v>-1.5566</v>
       </c>
       <c r="G16" t="n">
         <v>1.1219</v>
@@ -1702,13 +1702,13 @@
         <v>0.3895</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5626</v>
+        <v>-0.0526</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2999</v>
+        <v>0.0988</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2627</v>
+        <v>-0.1514</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2211</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7558</v>
+        <v>-0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0136</v>
+        <v>0.4848</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7422</v>
+        <v>-0.4918</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0215</v>
@@ -1780,13 +1780,13 @@
         <v>1.3632</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0974</v>
+        <v>-0.3486</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9275</v>
+        <v>-0.4291</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1699</v>
+        <v>0.0805</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7661</v>
+        <v>-0.3836</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6366</v>
+        <v>1.9357</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4028</v>
+        <v>-2.3193</v>
       </c>
       <c r="G18" t="n">
         <v>0.6788</v>
@@ -1858,13 +1858,13 @@
         <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.918</v>
+        <v>-0.5355</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4328</v>
+        <v>-0.1338</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4852</v>
+        <v>-0.4017</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5005</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9493</v>
+        <v>-3.0221</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4158</v>
+        <v>-1.0472</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5336</v>
+        <v>-1.9749</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.6724</v>
+        <v>-3.793</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.8291</v>
+        <v>-3.532</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8434</v>
+        <v>-0.261</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9146</v>
+        <v>-1.9181</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.1173</v>
+        <v>-2.4938</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2026</v>
+        <v>0.5757</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7578</v>
+        <v>-1.8749</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7118</v>
+        <v>-1.0381</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.046</v>
+        <v>-0.8368</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3632</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3632</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1389</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2778</v>
+        <v>0.312</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1389</v>
+        <v>-0.4047</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2211</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8751</v>
+        <v>-3.3086</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8446</v>
+        <v>-1.9141</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0305</v>
+        <v>-1.3944</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.793</v>
+        <v>-5.6724</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.532</v>
+        <v>-3.8291</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.261</v>
+        <v>-1.8434</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9181</v>
+        <v>-2.9146</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4938</v>
+        <v>-3.1173</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5757</v>
+        <v>0.2026</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8749</v>
+        <v>-2.7578</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0381</v>
+        <v>-0.7118</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8368</v>
+        <v>-2.046</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.3632</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9458</v>
+        <v>-0.2203</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4854</v>
+        <v>-0.2206</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4604</v>
+        <v>0.0002</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.2211</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6444</v>
+        <v>-5.0488</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.1238</v>
+        <v>-5.0273</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4794</v>
+        <v>-0.0215</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0764</v>
@@ -2092,13 +2092,13 @@
         <v>2.7263</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2038</v>
+        <v>0.3918</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1656</v>
+        <v>-0.0692</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9618</v>
+        <v>0.461</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1695</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.657800000000003</v>
+        <v>3.6576</v>
       </c>
       <c r="E22" t="n">
-        <v>10.7356</v>
+        <v>10.7359</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.078099999999999</v>
+        <v>-7.0782</v>
       </c>
       <c r="G22" t="n">
         <v>-8.5397</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0335</v>
+        <v>-1.033499999999999</v>
       </c>
       <c r="I22" t="n">
         <v>-7.5063</v>
@@ -2176,7 +2176,7 @@
         <v>1.357</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1105</v>
+        <v>0.1107</v>
       </c>
       <c r="V22" t="n">
         <v>0.9932000000000001</v>
